--- a/ZhC开发路线图 1.xlsx
+++ b/ZhC开发路线图 1.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="255">
   <si>
     <t>序号</t>
   </si>
@@ -751,6 +751,9 @@
     <t>异常捕获和处理</t>
   </si>
   <si>
+    <t>先提交 git，然后进行下一步开发。请把以下阶段的规划做成任务清单，逐个执行。 要求：每个任务开始前，必须先对照项目代码进行二次分析，核查开发文档的正确性，并挑选出有效的开发需求，进行开发。</t>
+  </si>
+  <si>
     <t>异常类型系统</t>
   </si>
   <si>
@@ -766,6 +769,9 @@
     <t>异常向上传播机制</t>
   </si>
   <si>
+    <t>请把以下阶段的规划做成任务清单，逐个执行。</t>
+  </si>
+  <si>
     <t>函数式</t>
   </si>
   <si>
@@ -775,10 +781,16 @@
     <t>闭包和 lambda 表达式</t>
   </si>
   <si>
+    <t>要求：每个任务开始前，必须先完成 详细的开发内容分析，以 优先级+功能模块+功能名称.md 文档保存到 docs/功能开发清单/</t>
+  </si>
+  <si>
     <t>协程支持</t>
   </si>
   <si>
     <t>异步函数和协程</t>
+  </si>
+  <si>
+    <t>优先级 功能模块 功能名称</t>
   </si>
   <si>
     <t>复数类型 _Complex</t>
@@ -3593,7 +3605,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:11">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3622,7 +3634,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:11">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3651,7 +3663,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:11">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3680,7 +3692,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:11">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3709,7 +3721,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:11">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3738,7 +3750,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:11">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3767,7 +3779,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:11">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3796,7 +3808,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:11">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3825,7 +3837,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:11">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3854,7 +3866,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:11">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3883,7 +3895,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:11">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3912,7 +3924,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:11">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3941,7 +3953,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:11">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3969,8 +3981,11 @@
       <c r="I61" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="62" spans="1:9">
+      <c r="J61" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
       <c r="A62">
         <v>61</v>
       </c>
@@ -3984,22 +3999,25 @@
         <v>183</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G62">
         <v>3</v>
       </c>
       <c r="H62" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I62" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="63" spans="1:9">
+      <c r="J62" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
       <c r="A63">
         <v>62</v>
       </c>
@@ -4013,22 +4031,28 @@
         <v>183</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G63">
         <v>3</v>
       </c>
       <c r="H63" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I63" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="64" spans="1:9">
+      <c r="J63" t="s">
+        <v>186</v>
+      </c>
+      <c r="K63" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
       <c r="A64">
         <v>63</v>
       </c>
@@ -4039,13 +4063,13 @@
         <v>182</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G64">
         <v>7</v>
@@ -4056,8 +4080,14 @@
       <c r="I64" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="65" spans="1:9">
+      <c r="J64" t="s">
+        <v>186</v>
+      </c>
+      <c r="K64" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
       <c r="A65">
         <v>64</v>
       </c>
@@ -4068,13 +4098,13 @@
         <v>182</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="G65">
         <v>8</v>
@@ -4085,8 +4115,14 @@
       <c r="I65" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="66" spans="1:9">
+      <c r="J65" t="s">
+        <v>186</v>
+      </c>
+      <c r="K65" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
       <c r="A66">
         <v>65</v>
       </c>
@@ -4100,10 +4136,10 @@
         <v>46</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G66">
         <v>4</v>
@@ -4114,8 +4150,11 @@
       <c r="I66" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="67" spans="1:9">
+      <c r="J66" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
       <c r="A67">
         <v>66</v>
       </c>
@@ -4129,10 +4168,10 @@
         <v>46</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G67">
         <v>4</v>
@@ -4143,8 +4182,11 @@
       <c r="I67" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="68" spans="1:9">
+      <c r="J67" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11">
       <c r="A68">
         <v>67</v>
       </c>
@@ -4155,13 +4197,13 @@
         <v>182</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G68">
         <v>6</v>
@@ -4172,8 +4214,11 @@
       <c r="I68" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="69" spans="1:9">
+      <c r="J68" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
       <c r="A69">
         <v>68</v>
       </c>
@@ -4184,25 +4229,28 @@
         <v>182</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G69">
         <v>4</v>
       </c>
       <c r="H69" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="I69" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="70" spans="1:9">
+      <c r="J69" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
       <c r="A70">
         <v>69</v>
       </c>
@@ -4213,13 +4261,13 @@
         <v>182</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E70" s="8" t="s">
         <v>180</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="G70">
         <v>5</v>
@@ -4230,8 +4278,11 @@
       <c r="I70" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="71" spans="1:9">
+      <c r="J70" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
       <c r="A71">
         <v>70</v>
       </c>
@@ -4242,13 +4293,13 @@
         <v>182</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="G71">
         <v>6</v>
@@ -4259,8 +4310,11 @@
       <c r="I71" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="72" spans="1:9">
+      <c r="J71" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
       <c r="A72">
         <v>71</v>
       </c>
@@ -4271,25 +4325,28 @@
         <v>182</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G72">
         <v>4</v>
       </c>
       <c r="H72" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I72" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="73" spans="1:9">
+      <c r="J72" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
       <c r="A73">
         <v>72</v>
       </c>
@@ -4300,42 +4357,45 @@
         <v>182</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="G73">
         <v>3</v>
       </c>
       <c r="H73" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I73" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="74" spans="1:9">
+      <c r="J73" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C74" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D74" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E74" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F74" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="G74">
         <v>5</v>
@@ -4347,82 +4407,82 @@
         <v>15</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:11">
       <c r="A75">
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C75" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D75" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E75" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F75" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G75">
         <v>4</v>
       </c>
       <c r="H75" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I75" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:11">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C76" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D76" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E76" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="F76" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="G76">
         <v>5</v>
       </c>
       <c r="H76" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I76" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:11">
       <c r="A77">
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C77" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D77" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="E77" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="F77" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="G77">
         <v>7</v>
@@ -4434,24 +4494,24 @@
         <v>15</v>
       </c>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:11">
       <c r="A78">
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C78" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D78" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E78" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="F78" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="G78">
         <v>7</v>
@@ -4463,24 +4523,24 @@
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:11">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C79" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D79" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E79" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="F79" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="G79">
         <v>10</v>
@@ -4492,24 +4552,24 @@
         <v>15</v>
       </c>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:11">
       <c r="A80">
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C80" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D80" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="E80" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="F80" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="G80">
         <v>4</v>
@@ -4526,19 +4586,19 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C81" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D81" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="E81" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="F81" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="G81">
         <v>3</v>
@@ -4555,19 +4615,19 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C82" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D82" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="E82" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F82" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="G82">
         <v>5</v>
@@ -4584,19 +4644,19 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C83" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D83" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E83" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F83" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="G83">
         <v>3</v>
@@ -4613,25 +4673,25 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C84" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D84" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E84" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="F84" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="G84">
         <v>3</v>
       </c>
       <c r="H84" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="I84" t="s">
         <v>15</v>
@@ -4642,25 +4702,25 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C85" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D85" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E85" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="F85" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="G85">
         <v>5</v>
       </c>
       <c r="H85" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="I85" t="s">
         <v>15</v>

--- a/ZhC开发路线图 1.xlsx
+++ b/ZhC开发路线图 1.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="259">
   <si>
     <t>序号</t>
   </si>
@@ -751,7 +751,14 @@
     <t>异常捕获和处理</t>
   </si>
   <si>
-    <t>先提交 git，然后进行下一步开发。请把以下阶段的规划做成任务清单，逐个执行。 要求：每个任务开始前，必须先对照项目代码进行二次分析，核查开发文档的正确性，并挑选出有效的开发需求，进行开发。</t>
+    <t>待完成
+LLVM EH intrinsics 集成（landingpad, resume）
+IR Generator 中生成异常处理 IR 节点
+与现有变量声明/作用域的完整集成
+单元测试</t>
+  </si>
+  <si>
+    <t>先提交 git，然后进行下一步开发。请把以下阶段的规划做成任务清单，逐个执行。 要求：每个任务开始前，必须先对照Zhc项目代码进行二次分析，核查开发文档的正确性，并挑选出有效的开发需求，进行开发。</t>
   </si>
   <si>
     <t>异常类型系统</t>
@@ -770,6 +777,59 @@
   </si>
   <si>
     <t>请把以下阶段的规划做成任务清单，逐个执行。</t>
+  </si>
+  <si>
+    <r>
+      <t>阶段</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">6: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>高级特性</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>自定义异常</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>并集成到语义分析器</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/IR</t>
+    </r>
+  </si>
+  <si>
+    <t>自定义异常类型支持，集成</t>
   </si>
   <si>
     <t>函数式</t>
@@ -1616,7 +1676,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1630,6 +1690,11 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2163,7 +2228,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N85"/>
+  <dimension ref="A1:O86"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -2173,10 +2238,12 @@
     <col min="5" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="40" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="9" width="10" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="39.84375" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" spans="1:14">
+    <row r="1" ht="18" customHeight="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2204,8 +2271,9 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2234,7 +2302,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2262,15 +2330,15 @@
       <c r="I3" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" s="4"/>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2298,13 +2366,13 @@
       <c r="I4" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="4"/>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" s="4"/>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2332,13 +2400,13 @@
       <c r="I5" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="4"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5" s="4"/>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2366,13 +2434,13 @@
       <c r="I6" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="4"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6" s="4"/>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2400,13 +2468,13 @@
       <c r="I7" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7" s="4"/>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2434,13 +2502,13 @@
       <c r="I8" t="s">
         <v>15</v>
       </c>
-      <c r="J8" s="4"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8" s="4"/>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2468,13 +2536,13 @@
       <c r="I9" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="4"/>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9" s="4"/>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2503,7 +2571,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:15">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2532,7 +2600,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:15">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2561,7 +2629,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:15">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2590,7 +2658,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:15">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2619,7 +2687,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:15">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2648,7 +2716,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:15">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3605,7 +3673,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:12">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3634,7 +3702,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:12">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3663,7 +3731,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:12">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3692,7 +3760,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:12">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3721,7 +3789,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:12">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3750,7 +3818,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:12">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3779,7 +3847,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:12">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3808,7 +3876,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:12">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3837,7 +3905,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:12">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3866,7 +3934,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:12">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3895,7 +3963,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:12">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3924,7 +3992,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:12">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3953,7 +4021,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" ht="15" customHeight="1" spans="1:12">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3978,14 +4046,14 @@
       <c r="H61" t="s">
         <v>14</v>
       </c>
-      <c r="I61" t="s">
-        <v>15</v>
-      </c>
-      <c r="J61" t="s">
+      <c r="I61" s="9" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="62" spans="1:11">
+      <c r="K61" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="62" ht="21" customHeight="1" spans="1:12">
       <c r="A62">
         <v>61</v>
       </c>
@@ -3999,25 +4067,23 @@
         <v>183</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G62">
         <v>3</v>
       </c>
       <c r="H62" t="s">
-        <v>189</v>
-      </c>
-      <c r="I62" t="s">
-        <v>15</v>
-      </c>
-      <c r="J62" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11">
+        <v>190</v>
+      </c>
+      <c r="I62" s="9"/>
+      <c r="K62" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="63" ht="17" customHeight="1" spans="1:12">
       <c r="A63">
         <v>62</v>
       </c>
@@ -4031,65 +4097,49 @@
         <v>183</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G63">
         <v>3</v>
       </c>
       <c r="H63" t="s">
-        <v>189</v>
-      </c>
-      <c r="I63" t="s">
-        <v>15</v>
-      </c>
-      <c r="J63" t="s">
-        <v>186</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="I63" s="9"/>
       <c r="K63" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" t="s">
-        <v>181</v>
+        <v>187</v>
+      </c>
+      <c r="L63" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="64" ht="17" spans="1:12">
+      <c r="B64" s="10" t="s">
+        <v>194</v>
       </c>
       <c r="C64" s="8" t="s">
         <v>182</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="F64" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="E64" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="G64">
-        <v>7</v>
-      </c>
-      <c r="H64" t="s">
-        <v>14</v>
-      </c>
-      <c r="I64" t="s">
-        <v>15</v>
-      </c>
-      <c r="J64" t="s">
-        <v>186</v>
-      </c>
+      <c r="F64" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="I64" s="9"/>
       <c r="K64" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12">
       <c r="A65">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B65" t="s">
         <v>181</v>
@@ -4098,16 +4148,16 @@
         <v>182</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G65">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H65" t="s">
         <v>14</v>
@@ -4115,16 +4165,16 @@
       <c r="I65" t="s">
         <v>15</v>
       </c>
-      <c r="J65" t="s">
-        <v>186</v>
-      </c>
       <c r="K65" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11">
+        <v>187</v>
+      </c>
+      <c r="L65" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12">
       <c r="A66">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B66" t="s">
         <v>181</v>
@@ -4133,16 +4183,16 @@
         <v>182</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>46</v>
+        <v>197</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G66">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H66" t="s">
         <v>14</v>
@@ -4150,13 +4200,16 @@
       <c r="I66" t="s">
         <v>15</v>
       </c>
-      <c r="J66" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11">
+      <c r="K66" t="s">
+        <v>187</v>
+      </c>
+      <c r="L66" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12">
       <c r="A67">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B67" t="s">
         <v>181</v>
@@ -4168,10 +4221,10 @@
         <v>46</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G67">
         <v>4</v>
@@ -4182,13 +4235,13 @@
       <c r="I67" t="s">
         <v>15</v>
       </c>
-      <c r="J67" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11">
+      <c r="K67" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12">
       <c r="A68">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B68" t="s">
         <v>181</v>
@@ -4197,16 +4250,16 @@
         <v>182</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>204</v>
+        <v>46</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G68">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H68" t="s">
         <v>14</v>
@@ -4214,13 +4267,13 @@
       <c r="I68" t="s">
         <v>15</v>
       </c>
-      <c r="J68" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11">
+      <c r="K68" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12">
       <c r="A69">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B69" t="s">
         <v>181</v>
@@ -4229,30 +4282,30 @@
         <v>182</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G69">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H69" t="s">
-        <v>209</v>
+        <v>14</v>
       </c>
       <c r="I69" t="s">
         <v>15</v>
       </c>
-      <c r="J69" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11">
+      <c r="K69" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12">
       <c r="A70">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B70" t="s">
         <v>181</v>
@@ -4261,30 +4314,30 @@
         <v>182</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>180</v>
+        <v>211</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H70" t="s">
-        <v>14</v>
+        <v>213</v>
       </c>
       <c r="I70" t="s">
         <v>15</v>
       </c>
-      <c r="J70" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11">
+      <c r="K70" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12">
       <c r="A71">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B71" t="s">
         <v>181</v>
@@ -4293,16 +4346,16 @@
         <v>182</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H71" t="s">
         <v>14</v>
@@ -4310,13 +4363,13 @@
       <c r="I71" t="s">
         <v>15</v>
       </c>
-      <c r="J71" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11">
+      <c r="K71" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12">
       <c r="A72">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B72" t="s">
         <v>181</v>
@@ -4325,30 +4378,30 @@
         <v>182</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G72">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H72" t="s">
-        <v>216</v>
+        <v>14</v>
       </c>
       <c r="I72" t="s">
         <v>15</v>
       </c>
-      <c r="J72" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11">
+      <c r="K72" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12">
       <c r="A73">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B73" t="s">
         <v>181</v>
@@ -4357,161 +4410,164 @@
         <v>182</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G73">
+        <v>4</v>
+      </c>
+      <c r="H73" t="s">
+        <v>220</v>
+      </c>
+      <c r="I73" t="s">
+        <v>15</v>
+      </c>
+      <c r="K73" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12">
+      <c r="A74">
+        <v>72</v>
+      </c>
+      <c r="B74" t="s">
+        <v>181</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="G74">
         <v>3</v>
       </c>
-      <c r="H73" t="s">
-        <v>216</v>
-      </c>
-      <c r="I73" t="s">
-        <v>15</v>
-      </c>
-      <c r="J73" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11">
-      <c r="A74">
+      <c r="H74" t="s">
+        <v>220</v>
+      </c>
+      <c r="I74" t="s">
+        <v>15</v>
+      </c>
+      <c r="K74" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12">
+      <c r="A75">
         <v>73</v>
       </c>
-      <c r="B74" t="s">
-        <v>219</v>
-      </c>
-      <c r="C74" t="s">
-        <v>220</v>
-      </c>
-      <c r="D74" t="s">
-        <v>221</v>
-      </c>
-      <c r="E74" t="s">
-        <v>222</v>
-      </c>
-      <c r="F74" t="s">
+      <c r="B75" t="s">
         <v>223</v>
       </c>
-      <c r="G74">
+      <c r="C75" t="s">
+        <v>224</v>
+      </c>
+      <c r="D75" t="s">
+        <v>225</v>
+      </c>
+      <c r="E75" t="s">
+        <v>226</v>
+      </c>
+      <c r="F75" t="s">
+        <v>227</v>
+      </c>
+      <c r="G75">
         <v>5</v>
       </c>
-      <c r="H74" t="s">
+      <c r="H75" t="s">
         <v>14</v>
       </c>
-      <c r="I74" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11">
-      <c r="A75">
+      <c r="I75" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12">
+      <c r="A76">
         <v>74</v>
       </c>
-      <c r="B75" t="s">
-        <v>219</v>
-      </c>
-      <c r="C75" t="s">
-        <v>220</v>
-      </c>
-      <c r="D75" t="s">
-        <v>221</v>
-      </c>
-      <c r="E75" t="s">
+      <c r="B76" t="s">
+        <v>223</v>
+      </c>
+      <c r="C76" t="s">
         <v>224</v>
       </c>
-      <c r="F75" t="s">
+      <c r="D76" t="s">
         <v>225</v>
       </c>
-      <c r="G75">
+      <c r="E76" t="s">
+        <v>228</v>
+      </c>
+      <c r="F76" t="s">
+        <v>229</v>
+      </c>
+      <c r="G76">
         <v>4</v>
       </c>
-      <c r="H75" t="s">
-        <v>226</v>
-      </c>
-      <c r="I75" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11">
-      <c r="A76">
+      <c r="H76" t="s">
+        <v>230</v>
+      </c>
+      <c r="I76" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12">
+      <c r="A77">
         <v>75</v>
       </c>
-      <c r="B76" t="s">
-        <v>219</v>
-      </c>
-      <c r="C76" t="s">
-        <v>220</v>
-      </c>
-      <c r="D76" t="s">
-        <v>221</v>
-      </c>
-      <c r="E76" t="s">
-        <v>227</v>
-      </c>
-      <c r="F76" t="s">
-        <v>228</v>
-      </c>
-      <c r="G76">
+      <c r="B77" t="s">
+        <v>223</v>
+      </c>
+      <c r="C77" t="s">
+        <v>224</v>
+      </c>
+      <c r="D77" t="s">
+        <v>225</v>
+      </c>
+      <c r="E77" t="s">
+        <v>231</v>
+      </c>
+      <c r="F77" t="s">
+        <v>232</v>
+      </c>
+      <c r="G77">
         <v>5</v>
       </c>
-      <c r="H76" t="s">
-        <v>226</v>
-      </c>
-      <c r="I76" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11">
-      <c r="A77">
+      <c r="H77" t="s">
+        <v>230</v>
+      </c>
+      <c r="I77" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12">
+      <c r="A78">
         <v>76</v>
       </c>
-      <c r="B77" t="s">
-        <v>219</v>
-      </c>
-      <c r="C77" t="s">
-        <v>220</v>
-      </c>
-      <c r="D77" t="s">
-        <v>229</v>
-      </c>
-      <c r="E77" t="s">
-        <v>230</v>
-      </c>
-      <c r="F77" t="s">
-        <v>231</v>
-      </c>
-      <c r="G77">
-        <v>7</v>
-      </c>
-      <c r="H77" t="s">
-        <v>14</v>
-      </c>
-      <c r="I77" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11">
-      <c r="A78">
-        <v>77</v>
-      </c>
       <c r="B78" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C78" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D78" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E78" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F78" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G78">
         <v>7</v>
@@ -4523,27 +4579,27 @@
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:12">
       <c r="A79">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C79" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D79" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E79" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F79" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G79">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H79" t="s">
         <v>14</v>
@@ -4552,27 +4608,27 @@
         <v>15</v>
       </c>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:12">
       <c r="A80">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="C80" t="s">
+        <v>224</v>
+      </c>
+      <c r="D80" t="s">
         <v>239</v>
       </c>
-      <c r="D80" t="s">
+      <c r="E80" t="s">
         <v>240</v>
       </c>
-      <c r="E80" t="s">
+      <c r="F80" t="s">
         <v>241</v>
       </c>
-      <c r="F80" t="s">
-        <v>242</v>
-      </c>
       <c r="G80">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H80" t="s">
         <v>14</v>
@@ -4583,25 +4639,25 @@
     </row>
     <row r="81" spans="1:9">
       <c r="A81">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C81" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D81" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E81" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F81" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G81">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H81" t="s">
         <v>14</v>
@@ -4612,25 +4668,25 @@
     </row>
     <row r="82" spans="1:9">
       <c r="A82">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C82" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D82" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E82" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F82" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G82">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H82" t="s">
         <v>14</v>
@@ -4641,25 +4697,25 @@
     </row>
     <row r="83" spans="1:9">
       <c r="A83">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C83" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D83" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E83" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F83" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G83">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H83" t="s">
         <v>14</v>
@@ -4670,28 +4726,28 @@
     </row>
     <row r="84" spans="1:9">
       <c r="A84">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C84" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D84" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E84" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F84" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G84">
         <v>3</v>
       </c>
       <c r="H84" t="s">
-        <v>252</v>
+        <v>14</v>
       </c>
       <c r="I84" t="s">
         <v>15</v>
@@ -4699,36 +4755,65 @@
     </row>
     <row r="85" spans="1:9">
       <c r="A85">
+        <v>83</v>
+      </c>
+      <c r="B85" t="s">
+        <v>242</v>
+      </c>
+      <c r="C85" t="s">
+        <v>243</v>
+      </c>
+      <c r="D85" t="s">
+        <v>251</v>
+      </c>
+      <c r="E85" t="s">
+        <v>254</v>
+      </c>
+      <c r="F85" t="s">
+        <v>255</v>
+      </c>
+      <c r="G85">
+        <v>3</v>
+      </c>
+      <c r="H85" t="s">
+        <v>256</v>
+      </c>
+      <c r="I85" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
+      <c r="A86">
         <v>84</v>
       </c>
-      <c r="B85" t="s">
-        <v>238</v>
-      </c>
-      <c r="C85" t="s">
-        <v>239</v>
-      </c>
-      <c r="D85" t="s">
-        <v>247</v>
-      </c>
-      <c r="E85" t="s">
-        <v>253</v>
-      </c>
-      <c r="F85" t="s">
-        <v>254</v>
-      </c>
-      <c r="G85">
+      <c r="B86" t="s">
+        <v>242</v>
+      </c>
+      <c r="C86" t="s">
+        <v>243</v>
+      </c>
+      <c r="D86" t="s">
+        <v>251</v>
+      </c>
+      <c r="E86" t="s">
+        <v>257</v>
+      </c>
+      <c r="F86" t="s">
+        <v>258</v>
+      </c>
+      <c r="G86">
         <v>5</v>
       </c>
-      <c r="H85" t="s">
-        <v>252</v>
-      </c>
-      <c r="I85" t="s">
+      <c r="H86" t="s">
+        <v>256</v>
+      </c>
+      <c r="I86" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="J3:N9"/>
+    <mergeCell ref="K3:O9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/ZhC开发路线图 1.xlsx
+++ b/ZhC开发路线图 1.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="259">
   <si>
     <t>序号</t>
   </si>
@@ -74,7 +74,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>待开发</t>
+    <t>开发完成</t>
   </si>
   <si>
     <t>ANSI 转义序列</t>
@@ -751,13 +751,6 @@
     <t>异常捕获和处理</t>
   </si>
   <si>
-    <t>待完成
-LLVM EH intrinsics 集成（landingpad, resume）
-IR Generator 中生成异常处理 IR 节点
-与现有变量声明/作用域的完整集成
-单元测试</t>
-  </si>
-  <si>
     <t>先提交 git，然后进行下一步开发。请把以下阶段的规划做成任务清单，逐个执行。 要求：每个任务开始前，必须先对照Zhc项目代码进行二次分析，核查开发文档的正确性，并挑选出有效的开发需求，进行开发。</t>
   </si>
   <si>
@@ -859,6 +852,9 @@
     <t>C99 复数类型支持</t>
   </si>
   <si>
+    <t>待开发</t>
+  </si>
+  <si>
     <t>定点数类型</t>
   </si>
   <si>
@@ -1028,7 +1024,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1043,6 +1039,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="宋体-简"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体-简"/>
       <charset val="134"/>
     </font>
@@ -1531,148 +1533,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1680,6 +1682,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1690,11 +1693,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2298,7 +2298,7 @@
       <c r="H2" t="s">
         <v>14</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2327,16 +2327,16 @@
       <c r="H3" t="s">
         <v>18</v>
       </c>
-      <c r="I3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K3" s="3" t="s">
+      <c r="I3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4">
@@ -2363,14 +2363,14 @@
       <c r="H4" t="s">
         <v>14</v>
       </c>
-      <c r="I4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
+      <c r="I4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5">
@@ -2397,14 +2397,14 @@
       <c r="H5" t="s">
         <v>25</v>
       </c>
-      <c r="I5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
+      <c r="I5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6">
@@ -2431,14 +2431,14 @@
       <c r="H6" t="s">
         <v>25</v>
       </c>
-      <c r="I6" t="s">
-        <v>15</v>
-      </c>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
+      <c r="I6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7">
@@ -2465,14 +2465,14 @@
       <c r="H7" t="s">
         <v>14</v>
       </c>
-      <c r="I7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
+      <c r="I7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8">
@@ -2499,14 +2499,14 @@
       <c r="H8" t="s">
         <v>33</v>
       </c>
-      <c r="I8" t="s">
-        <v>15</v>
-      </c>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
+      <c r="I8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9">
@@ -2533,14 +2533,14 @@
       <c r="H9" t="s">
         <v>33</v>
       </c>
-      <c r="I9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
+      <c r="I9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10">
@@ -2549,16 +2549,16 @@
       <c r="B10" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="6" t="s">
         <v>40</v>
       </c>
       <c r="G10">
@@ -2567,7 +2567,7 @@
       <c r="H10" t="s">
         <v>14</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2578,16 +2578,16 @@
       <c r="B11" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="6" t="s">
         <v>42</v>
       </c>
       <c r="G11">
@@ -2596,7 +2596,7 @@
       <c r="H11" t="s">
         <v>43</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2607,16 +2607,16 @@
       <c r="B12" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="6" t="s">
         <v>45</v>
       </c>
       <c r="G12">
@@ -2625,7 +2625,7 @@
       <c r="H12" t="s">
         <v>43</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I12" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2636,16 +2636,16 @@
       <c r="B13" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="6" t="s">
         <v>48</v>
       </c>
       <c r="G13">
@@ -2654,7 +2654,7 @@
       <c r="H13" t="s">
         <v>14</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2665,16 +2665,16 @@
       <c r="B14" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="6" t="s">
         <v>50</v>
       </c>
       <c r="G14">
@@ -2683,7 +2683,7 @@
       <c r="H14" t="s">
         <v>51</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2694,16 +2694,16 @@
       <c r="B15" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="6" t="s">
         <v>53</v>
       </c>
       <c r="G15">
@@ -2712,7 +2712,7 @@
       <c r="H15" t="s">
         <v>14</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I15" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2723,16 +2723,16 @@
       <c r="B16" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="6" t="s">
         <v>55</v>
       </c>
       <c r="G16">
@@ -2741,7 +2741,7 @@
       <c r="H16" t="s">
         <v>14</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I16" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2752,16 +2752,16 @@
       <c r="B17" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="6" t="s">
         <v>57</v>
       </c>
       <c r="G17">
@@ -2770,7 +2770,7 @@
       <c r="H17" t="s">
         <v>14</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I17" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2781,16 +2781,16 @@
       <c r="B18" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G18">
@@ -2799,7 +2799,7 @@
       <c r="H18" t="s">
         <v>14</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I18" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2810,16 +2810,16 @@
       <c r="B19" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="6" t="s">
         <v>62</v>
       </c>
       <c r="G19">
@@ -2828,7 +2828,7 @@
       <c r="H19" t="s">
         <v>63</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I19" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2839,16 +2839,16 @@
       <c r="B20" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="7" t="s">
         <v>68</v>
       </c>
       <c r="G20">
@@ -2857,7 +2857,7 @@
       <c r="H20" t="s">
         <v>14</v>
       </c>
-      <c r="I20" t="s">
+      <c r="I20" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2868,16 +2868,16 @@
       <c r="B21" t="s">
         <v>64</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" s="7" t="s">
         <v>70</v>
       </c>
       <c r="G21">
@@ -2886,7 +2886,7 @@
       <c r="H21" t="s">
         <v>14</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I21" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2897,16 +2897,16 @@
       <c r="B22" t="s">
         <v>64</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="7" t="s">
         <v>73</v>
       </c>
       <c r="G22">
@@ -2915,7 +2915,7 @@
       <c r="H22" t="s">
         <v>14</v>
       </c>
-      <c r="I22" t="s">
+      <c r="I22" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2926,16 +2926,16 @@
       <c r="B23" t="s">
         <v>64</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="7" t="s">
         <v>76</v>
       </c>
       <c r="G23">
@@ -2944,7 +2944,7 @@
       <c r="H23" t="s">
         <v>77</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2955,16 +2955,16 @@
       <c r="B24" t="s">
         <v>64</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="7" t="s">
         <v>80</v>
       </c>
       <c r="G24">
@@ -2973,7 +2973,7 @@
       <c r="H24" t="s">
         <v>81</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I24" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2984,16 +2984,16 @@
       <c r="B25" t="s">
         <v>64</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="F25" s="7" t="s">
         <v>84</v>
       </c>
       <c r="G25">
@@ -3002,7 +3002,7 @@
       <c r="H25" t="s">
         <v>77</v>
       </c>
-      <c r="I25" t="s">
+      <c r="I25" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3013,16 +3013,16 @@
       <c r="B26" t="s">
         <v>64</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="7" t="s">
         <v>87</v>
       </c>
       <c r="G26">
@@ -3031,7 +3031,7 @@
       <c r="H26" t="s">
         <v>14</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I26" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3042,16 +3042,16 @@
       <c r="B27" t="s">
         <v>64</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F27" s="7" t="s">
         <v>89</v>
       </c>
       <c r="G27">
@@ -3060,7 +3060,7 @@
       <c r="H27" t="s">
         <v>90</v>
       </c>
-      <c r="I27" t="s">
+      <c r="I27" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3071,16 +3071,16 @@
       <c r="B28" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F28" s="7" t="s">
         <v>92</v>
       </c>
       <c r="G28">
@@ -3089,7 +3089,7 @@
       <c r="H28" t="s">
         <v>93</v>
       </c>
-      <c r="I28" t="s">
+      <c r="I28" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
       <c r="H29" t="s">
         <v>14</v>
       </c>
-      <c r="I29" t="s">
+      <c r="I29" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
       <c r="H30" t="s">
         <v>14</v>
       </c>
-      <c r="I30" t="s">
+      <c r="I30" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       <c r="H31" t="s">
         <v>103</v>
       </c>
-      <c r="I31" t="s">
+      <c r="I31" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
       <c r="H32" t="s">
         <v>103</v>
       </c>
-      <c r="I32" t="s">
+      <c r="I32" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
       <c r="H33" t="s">
         <v>14</v>
       </c>
-      <c r="I33" t="s">
+      <c r="I33" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       <c r="H34" t="s">
         <v>111</v>
       </c>
-      <c r="I34" t="s">
+      <c r="I34" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3292,7 +3292,7 @@
       <c r="H35" t="s">
         <v>111</v>
       </c>
-      <c r="I35" t="s">
+      <c r="I35" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3321,7 +3321,7 @@
       <c r="H36" t="s">
         <v>14</v>
       </c>
-      <c r="I36" t="s">
+      <c r="I36" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       <c r="H37" t="s">
         <v>119</v>
       </c>
-      <c r="I37" t="s">
+      <c r="I37" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3379,7 +3379,7 @@
       <c r="H38" t="s">
         <v>119</v>
       </c>
-      <c r="I38" t="s">
+      <c r="I38" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       <c r="H39" t="s">
         <v>14</v>
       </c>
-      <c r="I39" t="s">
+      <c r="I39" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3437,7 +3437,7 @@
       <c r="H40" t="s">
         <v>127</v>
       </c>
-      <c r="I40" t="s">
+      <c r="I40" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3466,7 +3466,7 @@
       <c r="H41" t="s">
         <v>127</v>
       </c>
-      <c r="I41" t="s">
+      <c r="I41" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3495,7 +3495,7 @@
       <c r="H42" t="s">
         <v>14</v>
       </c>
-      <c r="I42" t="s">
+      <c r="I42" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3524,7 +3524,7 @@
       <c r="H43" t="s">
         <v>135</v>
       </c>
-      <c r="I43" t="s">
+      <c r="I43" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3553,7 +3553,7 @@
       <c r="H44" t="s">
         <v>135</v>
       </c>
-      <c r="I44" t="s">
+      <c r="I44" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3582,7 +3582,7 @@
       <c r="H45" t="s">
         <v>14</v>
       </c>
-      <c r="I45" t="s">
+      <c r="I45" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       <c r="H46" t="s">
         <v>14</v>
       </c>
-      <c r="I46" t="s">
+      <c r="I46" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       <c r="H47" t="s">
         <v>14</v>
       </c>
-      <c r="I47" t="s">
+      <c r="I47" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
       <c r="H48" t="s">
         <v>14</v>
       </c>
-      <c r="I48" t="s">
+      <c r="I48" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3680,16 +3680,16 @@
       <c r="B49" t="s">
         <v>147</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="C49" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="D49" s="7" t="s">
+      <c r="D49" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="E49" s="7" t="s">
+      <c r="E49" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="F49" s="7" t="s">
+      <c r="F49" s="8" t="s">
         <v>151</v>
       </c>
       <c r="G49">
@@ -3698,7 +3698,7 @@
       <c r="H49" t="s">
         <v>14</v>
       </c>
-      <c r="I49" t="s">
+      <c r="I49" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3709,16 +3709,16 @@
       <c r="B50" t="s">
         <v>147</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C50" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="D50" s="7" t="s">
+      <c r="D50" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="E50" s="7" t="s">
+      <c r="E50" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="F50" s="7" t="s">
+      <c r="F50" s="8" t="s">
         <v>153</v>
       </c>
       <c r="G50">
@@ -3727,7 +3727,7 @@
       <c r="H50" t="s">
         <v>154</v>
       </c>
-      <c r="I50" t="s">
+      <c r="I50" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3738,16 +3738,16 @@
       <c r="B51" t="s">
         <v>147</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C51" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="D51" s="7" t="s">
+      <c r="D51" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="E51" s="7" t="s">
+      <c r="E51" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="F51" s="7" t="s">
+      <c r="F51" s="8" t="s">
         <v>156</v>
       </c>
       <c r="G51">
@@ -3756,7 +3756,7 @@
       <c r="H51" t="s">
         <v>154</v>
       </c>
-      <c r="I51" t="s">
+      <c r="I51" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3767,16 +3767,16 @@
       <c r="B52" t="s">
         <v>147</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C52" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="D52" s="7" t="s">
+      <c r="D52" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="E52" s="7" t="s">
+      <c r="E52" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="F52" s="7" t="s">
+      <c r="F52" s="8" t="s">
         <v>159</v>
       </c>
       <c r="G52">
@@ -3785,7 +3785,7 @@
       <c r="H52" t="s">
         <v>14</v>
       </c>
-      <c r="I52" t="s">
+      <c r="I52" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3796,16 +3796,16 @@
       <c r="B53" t="s">
         <v>147</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C53" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="D53" s="7" t="s">
+      <c r="D53" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="E53" s="7" t="s">
+      <c r="E53" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="F53" s="7" t="s">
+      <c r="F53" s="8" t="s">
         <v>161</v>
       </c>
       <c r="G53">
@@ -3814,7 +3814,7 @@
       <c r="H53" t="s">
         <v>162</v>
       </c>
-      <c r="I53" t="s">
+      <c r="I53" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3825,16 +3825,16 @@
       <c r="B54" t="s">
         <v>147</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C54" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="D54" s="7" t="s">
+      <c r="D54" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="E54" s="7" t="s">
+      <c r="E54" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="F54" s="7" t="s">
+      <c r="F54" s="8" t="s">
         <v>164</v>
       </c>
       <c r="G54">
@@ -3843,7 +3843,7 @@
       <c r="H54" t="s">
         <v>162</v>
       </c>
-      <c r="I54" t="s">
+      <c r="I54" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3854,16 +3854,16 @@
       <c r="B55" t="s">
         <v>147</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C55" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="D55" s="7" t="s">
+      <c r="D55" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="E55" s="7" t="s">
+      <c r="E55" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="F55" s="7" t="s">
+      <c r="F55" s="8" t="s">
         <v>167</v>
       </c>
       <c r="G55">
@@ -3872,7 +3872,7 @@
       <c r="H55" t="s">
         <v>14</v>
       </c>
-      <c r="I55" t="s">
+      <c r="I55" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3883,16 +3883,16 @@
       <c r="B56" t="s">
         <v>147</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="C56" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="D56" s="7" t="s">
+      <c r="D56" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="E56" s="7" t="s">
+      <c r="E56" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="F56" s="7" t="s">
+      <c r="F56" s="8" t="s">
         <v>169</v>
       </c>
       <c r="G56">
@@ -3901,7 +3901,7 @@
       <c r="H56" t="s">
         <v>170</v>
       </c>
-      <c r="I56" t="s">
+      <c r="I56" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3912,16 +3912,16 @@
       <c r="B57" t="s">
         <v>147</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C57" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="D57" s="7" t="s">
+      <c r="D57" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="E57" s="7" t="s">
+      <c r="E57" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="F57" s="7" t="s">
+      <c r="F57" s="8" t="s">
         <v>172</v>
       </c>
       <c r="G57">
@@ -3930,7 +3930,7 @@
       <c r="H57" t="s">
         <v>170</v>
       </c>
-      <c r="I57" t="s">
+      <c r="I57" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3941,16 +3941,16 @@
       <c r="B58" t="s">
         <v>147</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C58" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="D58" s="7" t="s">
+      <c r="D58" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="E58" s="7" t="s">
+      <c r="E58" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="F58" s="7" t="s">
+      <c r="F58" s="8" t="s">
         <v>175</v>
       </c>
       <c r="G58">
@@ -3959,7 +3959,7 @@
       <c r="H58" t="s">
         <v>14</v>
       </c>
-      <c r="I58" t="s">
+      <c r="I58" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3970,16 +3970,16 @@
       <c r="B59" t="s">
         <v>147</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C59" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="D59" s="7" t="s">
+      <c r="D59" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="E59" s="7" t="s">
+      <c r="E59" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="F59" s="7" t="s">
+      <c r="F59" s="8" t="s">
         <v>177</v>
       </c>
       <c r="G59">
@@ -3988,7 +3988,7 @@
       <c r="H59" t="s">
         <v>178</v>
       </c>
-      <c r="I59" t="s">
+      <c r="I59" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3999,16 +3999,16 @@
       <c r="B60" t="s">
         <v>147</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C60" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="D60" s="7" t="s">
+      <c r="D60" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="E60" s="7" t="s">
+      <c r="E60" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="F60" s="7" t="s">
+      <c r="F60" s="8" t="s">
         <v>180</v>
       </c>
       <c r="G60">
@@ -4017,7 +4017,7 @@
       <c r="H60" t="s">
         <v>178</v>
       </c>
-      <c r="I60" t="s">
+      <c r="I60" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4028,16 +4028,16 @@
       <c r="B61" t="s">
         <v>181</v>
       </c>
-      <c r="C61" s="8" t="s">
+      <c r="C61" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="D61" s="8" t="s">
+      <c r="D61" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="E61" s="8" t="s">
+      <c r="E61" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="F61" s="8" t="s">
+      <c r="F61" s="9" t="s">
         <v>185</v>
       </c>
       <c r="G61">
@@ -4046,11 +4046,11 @@
       <c r="H61" t="s">
         <v>14</v>
       </c>
-      <c r="I61" s="9" t="s">
+      <c r="I61" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K61" t="s">
         <v>186</v>
-      </c>
-      <c r="K61" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="62" ht="21" customHeight="1" spans="1:12">
@@ -4060,27 +4060,29 @@
       <c r="B62" t="s">
         <v>181</v>
       </c>
-      <c r="C62" s="8" t="s">
+      <c r="C62" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="D62" s="8" t="s">
+      <c r="D62" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="E62" s="8" t="s">
+      <c r="E62" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="F62" s="9" t="s">
         <v>188</v>
-      </c>
-      <c r="F62" s="8" t="s">
-        <v>189</v>
       </c>
       <c r="G62">
         <v>3</v>
       </c>
       <c r="H62" t="s">
-        <v>190</v>
-      </c>
-      <c r="I62" s="9"/>
+        <v>189</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="K62" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="63" ht="17" customHeight="1" spans="1:12">
@@ -4090,51 +4092,55 @@
       <c r="B63" t="s">
         <v>181</v>
       </c>
-      <c r="C63" s="8" t="s">
+      <c r="C63" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="D63" s="8" t="s">
+      <c r="D63" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="E63" s="8" t="s">
+      <c r="E63" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="F63" s="9" t="s">
         <v>191</v>
-      </c>
-      <c r="F63" s="8" t="s">
-        <v>192</v>
       </c>
       <c r="G63">
         <v>3</v>
       </c>
       <c r="H63" t="s">
-        <v>190</v>
-      </c>
-      <c r="I63" s="9"/>
+        <v>189</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="K63" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L63" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="64" ht="17" spans="1:12">
+      <c r="B64" s="3" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="64" ht="17" spans="1:12">
-      <c r="B64" s="10" t="s">
+      <c r="C64" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="E64" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="C64" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="D64" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="E64" s="11" t="s">
+      <c r="F64" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="F64" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="I64" s="9"/>
+      <c r="I64" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="K64" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -4144,17 +4150,17 @@
       <c r="B65" t="s">
         <v>181</v>
       </c>
-      <c r="C65" s="8" t="s">
+      <c r="C65" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="D65" s="8" t="s">
+      <c r="D65" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="E65" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="E65" s="8" t="s">
+      <c r="F65" s="9" t="s">
         <v>198</v>
-      </c>
-      <c r="F65" s="8" t="s">
-        <v>199</v>
       </c>
       <c r="G65">
         <v>7</v>
@@ -4162,14 +4168,14 @@
       <c r="H65" t="s">
         <v>14</v>
       </c>
-      <c r="I65" t="s">
+      <c r="I65" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K65" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L65" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -4179,17 +4185,17 @@
       <c r="B66" t="s">
         <v>181</v>
       </c>
-      <c r="C66" s="8" t="s">
+      <c r="C66" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="D66" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="E66" s="8" t="s">
+      <c r="D66" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="E66" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="F66" s="9" t="s">
         <v>201</v>
-      </c>
-      <c r="F66" s="8" t="s">
-        <v>202</v>
       </c>
       <c r="G66">
         <v>8</v>
@@ -4197,14 +4203,14 @@
       <c r="H66" t="s">
         <v>14</v>
       </c>
-      <c r="I66" t="s">
+      <c r="I66" s="3" t="s">
         <v>15</v>
       </c>
       <c r="K66" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L66" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="67" spans="1:12">
@@ -4214,17 +4220,17 @@
       <c r="B67" t="s">
         <v>181</v>
       </c>
-      <c r="C67" s="8" t="s">
+      <c r="C67" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="D67" s="8" t="s">
+      <c r="D67" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="E67" s="8" t="s">
+      <c r="E67" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="F67" s="9" t="s">
         <v>204</v>
-      </c>
-      <c r="F67" s="8" t="s">
-        <v>205</v>
       </c>
       <c r="G67">
         <v>4</v>
@@ -4232,11 +4238,11 @@
       <c r="H67" t="s">
         <v>14</v>
       </c>
-      <c r="I67" t="s">
-        <v>15</v>
+      <c r="I67" s="11" t="s">
+        <v>205</v>
       </c>
       <c r="K67" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="68" spans="1:12">
@@ -4246,16 +4252,16 @@
       <c r="B68" t="s">
         <v>181</v>
       </c>
-      <c r="C68" s="8" t="s">
+      <c r="C68" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="D68" s="8" t="s">
+      <c r="D68" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="E68" s="8" t="s">
+      <c r="E68" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="F68" s="8" t="s">
+      <c r="F68" s="9" t="s">
         <v>207</v>
       </c>
       <c r="G68">
@@ -4264,11 +4270,11 @@
       <c r="H68" t="s">
         <v>14</v>
       </c>
-      <c r="I68" t="s">
-        <v>15</v>
+      <c r="I68" s="11" t="s">
+        <v>205</v>
       </c>
       <c r="K68" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -4278,16 +4284,16 @@
       <c r="B69" t="s">
         <v>181</v>
       </c>
-      <c r="C69" s="8" t="s">
+      <c r="C69" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="D69" s="8" t="s">
+      <c r="D69" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="E69" s="8" t="s">
+      <c r="E69" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="F69" s="8" t="s">
+      <c r="F69" s="9" t="s">
         <v>210</v>
       </c>
       <c r="G69">
@@ -4296,11 +4302,11 @@
       <c r="H69" t="s">
         <v>14</v>
       </c>
-      <c r="I69" t="s">
-        <v>15</v>
+      <c r="I69" s="11" t="s">
+        <v>205</v>
       </c>
       <c r="K69" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="70" spans="1:12">
@@ -4310,16 +4316,16 @@
       <c r="B70" t="s">
         <v>181</v>
       </c>
-      <c r="C70" s="8" t="s">
+      <c r="C70" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="D70" s="8" t="s">
+      <c r="D70" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="E70" s="8" t="s">
+      <c r="E70" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="F70" s="8" t="s">
+      <c r="F70" s="9" t="s">
         <v>212</v>
       </c>
       <c r="G70">
@@ -4328,11 +4334,11 @@
       <c r="H70" t="s">
         <v>213</v>
       </c>
-      <c r="I70" t="s">
-        <v>15</v>
+      <c r="I70" s="11" t="s">
+        <v>205</v>
       </c>
       <c r="K70" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="71" spans="1:12">
@@ -4342,16 +4348,16 @@
       <c r="B71" t="s">
         <v>181</v>
       </c>
-      <c r="C71" s="8" t="s">
+      <c r="C71" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="D71" s="8" t="s">
+      <c r="D71" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="E71" s="8" t="s">
+      <c r="E71" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="F71" s="8" t="s">
+      <c r="F71" s="9" t="s">
         <v>214</v>
       </c>
       <c r="G71">
@@ -4360,11 +4366,11 @@
       <c r="H71" t="s">
         <v>14</v>
       </c>
-      <c r="I71" t="s">
-        <v>15</v>
+      <c r="I71" s="11" t="s">
+        <v>205</v>
       </c>
       <c r="K71" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="72" spans="1:12">
@@ -4374,16 +4380,16 @@
       <c r="B72" t="s">
         <v>181</v>
       </c>
-      <c r="C72" s="8" t="s">
+      <c r="C72" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="D72" s="8" t="s">
+      <c r="D72" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="E72" s="8" t="s">
+      <c r="E72" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="F72" s="8" t="s">
+      <c r="F72" s="9" t="s">
         <v>217</v>
       </c>
       <c r="G72">
@@ -4392,11 +4398,11 @@
       <c r="H72" t="s">
         <v>14</v>
       </c>
-      <c r="I72" t="s">
-        <v>15</v>
+      <c r="I72" s="11" t="s">
+        <v>205</v>
       </c>
       <c r="K72" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -4406,16 +4412,16 @@
       <c r="B73" t="s">
         <v>181</v>
       </c>
-      <c r="C73" s="8" t="s">
+      <c r="C73" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="D73" s="8" t="s">
+      <c r="D73" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="E73" s="8" t="s">
+      <c r="E73" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="F73" s="8" t="s">
+      <c r="F73" s="9" t="s">
         <v>219</v>
       </c>
       <c r="G73">
@@ -4424,11 +4430,11 @@
       <c r="H73" t="s">
         <v>220</v>
       </c>
-      <c r="I73" t="s">
-        <v>15</v>
+      <c r="I73" s="11" t="s">
+        <v>205</v>
       </c>
       <c r="K73" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -4438,16 +4444,16 @@
       <c r="B74" t="s">
         <v>181</v>
       </c>
-      <c r="C74" s="8" t="s">
+      <c r="C74" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="D74" s="8" t="s">
+      <c r="D74" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="E74" s="8" t="s">
+      <c r="E74" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="F74" s="8" t="s">
+      <c r="F74" s="9" t="s">
         <v>222</v>
       </c>
       <c r="G74">
@@ -4456,11 +4462,11 @@
       <c r="H74" t="s">
         <v>220</v>
       </c>
-      <c r="I74" t="s">
-        <v>15</v>
+      <c r="I74" s="11" t="s">
+        <v>205</v>
       </c>
       <c r="K74" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -4488,8 +4494,8 @@
       <c r="H75" t="s">
         <v>14</v>
       </c>
-      <c r="I75" t="s">
-        <v>15</v>
+      <c r="I75" s="11" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="76" spans="1:12">
@@ -4517,8 +4523,8 @@
       <c r="H76" t="s">
         <v>230</v>
       </c>
-      <c r="I76" t="s">
-        <v>15</v>
+      <c r="I76" s="11" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -4546,8 +4552,8 @@
       <c r="H77" t="s">
         <v>230</v>
       </c>
-      <c r="I77" t="s">
-        <v>15</v>
+      <c r="I77" s="11" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -4575,8 +4581,8 @@
       <c r="H78" t="s">
         <v>14</v>
       </c>
-      <c r="I78" t="s">
-        <v>15</v>
+      <c r="I78" s="11" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -4604,8 +4610,8 @@
       <c r="H79" t="s">
         <v>14</v>
       </c>
-      <c r="I79" t="s">
-        <v>15</v>
+      <c r="I79" s="11" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -4633,8 +4639,8 @@
       <c r="H80" t="s">
         <v>14</v>
       </c>
-      <c r="I80" t="s">
-        <v>15</v>
+      <c r="I80" s="11" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -4662,8 +4668,8 @@
       <c r="H81" t="s">
         <v>14</v>
       </c>
-      <c r="I81" t="s">
-        <v>15</v>
+      <c r="I81" s="11" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -4691,8 +4697,8 @@
       <c r="H82" t="s">
         <v>14</v>
       </c>
-      <c r="I82" t="s">
-        <v>15</v>
+      <c r="I82" s="11" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -4720,8 +4726,8 @@
       <c r="H83" t="s">
         <v>14</v>
       </c>
-      <c r="I83" t="s">
-        <v>15</v>
+      <c r="I83" s="11" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -4749,8 +4755,8 @@
       <c r="H84" t="s">
         <v>14</v>
       </c>
-      <c r="I84" t="s">
-        <v>15</v>
+      <c r="I84" s="11" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -4778,8 +4784,8 @@
       <c r="H85" t="s">
         <v>256</v>
       </c>
-      <c r="I85" t="s">
-        <v>15</v>
+      <c r="I85" s="11" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -4807,8 +4813,8 @@
       <c r="H86" t="s">
         <v>256</v>
       </c>
-      <c r="I86" t="s">
-        <v>15</v>
+      <c r="I86" s="11" t="s">
+        <v>205</v>
       </c>
     </row>
   </sheetData>

--- a/ZhC开发路线图 1.xlsx
+++ b/ZhC开发路线图 1.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="260">
   <si>
     <t>序号</t>
   </si>
@@ -852,43 +852,46 @@
     <t>C99 复数类型支持</t>
   </si>
   <si>
+    <t>定点数类型</t>
+  </si>
+  <si>
+    <t>_Fract 和 _Accum 类型</t>
+  </si>
+  <si>
+    <t>内存管理</t>
+  </si>
+  <si>
+    <t>智能指针</t>
+  </si>
+  <si>
+    <t>unique_ptr/shared_ptr 类似功能</t>
+  </si>
+  <si>
+    <t>RAII 模式</t>
+  </si>
+  <si>
+    <t>资源获取即初始化</t>
+  </si>
+  <si>
+    <t>序号67</t>
+  </si>
+  <si>
+    <t>运行时内存泄漏检测</t>
+  </si>
+  <si>
+    <t>反射</t>
+  </si>
+  <si>
+    <t>类型信息查询</t>
+  </si>
+  <si>
+    <t>运行时类型信息</t>
+  </si>
+  <si>
     <t>待开发</t>
   </si>
   <si>
-    <t>定点数类型</t>
-  </si>
-  <si>
-    <t>_Fract 和 _Accum 类型</t>
-  </si>
-  <si>
-    <t>内存管理</t>
-  </si>
-  <si>
-    <t>智能指针</t>
-  </si>
-  <si>
-    <t>unique_ptr/shared_ptr 类似功能</t>
-  </si>
-  <si>
-    <t>RAII 模式</t>
-  </si>
-  <si>
-    <t>资源获取即初始化</t>
-  </si>
-  <si>
-    <t>序号67</t>
-  </si>
-  <si>
-    <t>运行时内存泄漏检测</t>
-  </si>
-  <si>
-    <t>反射</t>
-  </si>
-  <si>
-    <t>类型信息查询</t>
-  </si>
-  <si>
-    <t>运行时类型信息</t>
+    <t>我们需要程序编译器专家的帮助，帮助我们进行下一步开发。把以下阶段的规划做成任务清单，逐个执行。 要求：每个任务开始前，必须先对照Zhc项目代码进行二次分析，核查开发需求的正确性，并挑选出有效的开发需求，进行开发。</t>
   </si>
   <si>
     <t>运行时类型检查</t>
@@ -4238,8 +4241,8 @@
       <c r="H67" t="s">
         <v>14</v>
       </c>
-      <c r="I67" s="11" t="s">
-        <v>205</v>
+      <c r="I67" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="K67" t="s">
         <v>186</v>
@@ -4259,10 +4262,10 @@
         <v>46</v>
       </c>
       <c r="E68" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="F68" s="9" t="s">
         <v>206</v>
-      </c>
-      <c r="F68" s="9" t="s">
-        <v>207</v>
       </c>
       <c r="G68">
         <v>4</v>
@@ -4270,8 +4273,8 @@
       <c r="H68" t="s">
         <v>14</v>
       </c>
-      <c r="I68" s="11" t="s">
-        <v>205</v>
+      <c r="I68" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="K68" t="s">
         <v>186</v>
@@ -4288,13 +4291,13 @@
         <v>182</v>
       </c>
       <c r="D69" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="E69" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="E69" s="9" t="s">
+      <c r="F69" s="9" t="s">
         <v>209</v>
-      </c>
-      <c r="F69" s="9" t="s">
-        <v>210</v>
       </c>
       <c r="G69">
         <v>6</v>
@@ -4302,8 +4305,8 @@
       <c r="H69" t="s">
         <v>14</v>
       </c>
-      <c r="I69" s="11" t="s">
-        <v>205</v>
+      <c r="I69" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="K69" t="s">
         <v>186</v>
@@ -4320,22 +4323,22 @@
         <v>182</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E70" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="F70" s="9" t="s">
         <v>211</v>
-      </c>
-      <c r="F70" s="9" t="s">
-        <v>212</v>
       </c>
       <c r="G70">
         <v>4</v>
       </c>
       <c r="H70" t="s">
-        <v>213</v>
-      </c>
-      <c r="I70" s="11" t="s">
-        <v>205</v>
+        <v>212</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="K70" t="s">
         <v>186</v>
@@ -4352,13 +4355,13 @@
         <v>182</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>180</v>
       </c>
       <c r="F71" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G71">
         <v>5</v>
@@ -4366,8 +4369,8 @@
       <c r="H71" t="s">
         <v>14</v>
       </c>
-      <c r="I71" s="11" t="s">
-        <v>205</v>
+      <c r="I71" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="K71" t="s">
         <v>186</v>
@@ -4384,13 +4387,13 @@
         <v>182</v>
       </c>
       <c r="D72" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="E72" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="E72" s="9" t="s">
+      <c r="F72" s="9" t="s">
         <v>216</v>
-      </c>
-      <c r="F72" s="9" t="s">
-        <v>217</v>
       </c>
       <c r="G72">
         <v>6</v>
@@ -4399,10 +4402,10 @@
         <v>14</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="K72" t="s">
-        <v>186</v>
+        <v>218</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -4416,25 +4419,25 @@
         <v>182</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F73" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G73">
         <v>4</v>
       </c>
       <c r="H73" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="K73" t="s">
-        <v>186</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -4448,25 +4451,25 @@
         <v>182</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F74" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G74">
         <v>3</v>
       </c>
       <c r="H74" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="K74" t="s">
-        <v>186</v>
+        <v>218</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -4474,19 +4477,19 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C75" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D75" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E75" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F75" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G75">
         <v>5</v>
@@ -4495,7 +4498,10 @@
         <v>14</v>
       </c>
       <c r="I75" s="11" t="s">
-        <v>205</v>
+        <v>217</v>
+      </c>
+      <c r="K75" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="76" spans="1:12">
@@ -4503,28 +4509,31 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C76" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D76" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E76" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F76" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G76">
         <v>4</v>
       </c>
       <c r="H76" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I76" s="11" t="s">
-        <v>205</v>
+        <v>217</v>
+      </c>
+      <c r="K76" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -4532,28 +4541,31 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C77" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D77" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E77" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F77" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G77">
         <v>5</v>
       </c>
       <c r="H77" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I77" s="11" t="s">
-        <v>205</v>
+        <v>217</v>
+      </c>
+      <c r="K77" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -4561,19 +4573,19 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C78" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D78" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E78" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F78" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G78">
         <v>7</v>
@@ -4582,7 +4594,10 @@
         <v>14</v>
       </c>
       <c r="I78" s="11" t="s">
-        <v>205</v>
+        <v>217</v>
+      </c>
+      <c r="K78" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -4590,19 +4605,19 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C79" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D79" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E79" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F79" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G79">
         <v>7</v>
@@ -4611,7 +4626,10 @@
         <v>14</v>
       </c>
       <c r="I79" s="11" t="s">
-        <v>205</v>
+        <v>217</v>
+      </c>
+      <c r="K79" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -4619,19 +4637,19 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D80" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E80" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F80" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G80">
         <v>10</v>
@@ -4640,27 +4658,30 @@
         <v>14</v>
       </c>
       <c r="I80" s="11" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9">
+        <v>217</v>
+      </c>
+      <c r="K80" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11">
       <c r="A81">
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C81" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D81" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E81" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F81" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G81">
         <v>4</v>
@@ -4669,27 +4690,30 @@
         <v>14</v>
       </c>
       <c r="I81" s="11" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9">
+        <v>217</v>
+      </c>
+      <c r="K81" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
       <c r="A82">
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C82" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D82" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E82" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F82" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G82">
         <v>3</v>
@@ -4698,27 +4722,30 @@
         <v>14</v>
       </c>
       <c r="I82" s="11" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9">
+        <v>217</v>
+      </c>
+      <c r="K82" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11">
       <c r="A83">
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C83" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D83" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E83" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F83" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G83">
         <v>5</v>
@@ -4727,27 +4754,30 @@
         <v>14</v>
       </c>
       <c r="I83" s="11" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9">
+        <v>217</v>
+      </c>
+      <c r="K83" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
       <c r="A84">
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C84" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D84" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E84" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F84" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G84">
         <v>3</v>
@@ -4756,65 +4786,74 @@
         <v>14</v>
       </c>
       <c r="I84" s="11" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9">
+        <v>217</v>
+      </c>
+      <c r="K84" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11">
       <c r="A85">
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C85" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D85" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E85" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F85" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G85">
         <v>3</v>
       </c>
       <c r="H85" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I85" s="11" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9">
+        <v>217</v>
+      </c>
+      <c r="K85" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
       <c r="A86">
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C86" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D86" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E86" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F86" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G86">
         <v>5</v>
       </c>
       <c r="H86" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I86" s="11" t="s">
-        <v>205</v>
+        <v>217</v>
+      </c>
+      <c r="K86" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>

--- a/ZhC开发路线图 1.xlsx
+++ b/ZhC开发路线图 1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12320"/>
+    <workbookView windowWidth="17720" windowHeight="7440"/>
   </bookViews>
   <sheets>
     <sheet name="开发路线图" sheetId="1" r:id="rId1"/>
@@ -87,6 +87,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
       <t>请把以下阶段的规划做成任务清单，逐个执行。</t>
     </r>
     <r>
@@ -773,6 +778,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
       <t>阶段</t>
     </r>
     <r>
@@ -794,6 +804,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
       <t>自定义异常</t>
     </r>
     <r>
@@ -888,40 +903,40 @@
     <t>运行时类型信息</t>
   </si>
   <si>
+    <t>我们需要程序编译器专家的帮助，帮助我们进行下一步开发。把以下阶段的规划做成任务清单，逐个执行。 要求：每个任务开始前，必须先对照Zhc项目代码进行二次分析，核查开发需求的正确性，并挑选出有效的开发需求，进行开发。</t>
+  </si>
+  <si>
+    <t>运行时类型检查</t>
+  </si>
+  <si>
+    <t>动态类型检查</t>
+  </si>
+  <si>
+    <t>序号70</t>
+  </si>
+  <si>
+    <t>动态类型转换</t>
+  </si>
+  <si>
+    <t>安全的类型转换</t>
+  </si>
+  <si>
+    <t>阶段7: 后端支持</t>
+  </si>
+  <si>
+    <t>P6</t>
+  </si>
+  <si>
+    <t>WASM</t>
+  </si>
+  <si>
+    <t>WASM 特定优化</t>
+  </si>
+  <si>
+    <t>WebAssembly 优化</t>
+  </si>
+  <si>
     <t>待开发</t>
-  </si>
-  <si>
-    <t>我们需要程序编译器专家的帮助，帮助我们进行下一步开发。把以下阶段的规划做成任务清单，逐个执行。 要求：每个任务开始前，必须先对照Zhc项目代码进行二次分析，核查开发需求的正确性，并挑选出有效的开发需求，进行开发。</t>
-  </si>
-  <si>
-    <t>运行时类型检查</t>
-  </si>
-  <si>
-    <t>动态类型检查</t>
-  </si>
-  <si>
-    <t>序号70</t>
-  </si>
-  <si>
-    <t>动态类型转换</t>
-  </si>
-  <si>
-    <t>安全的类型转换</t>
-  </si>
-  <si>
-    <t>阶段7: 后端支持</t>
-  </si>
-  <si>
-    <t>P6</t>
-  </si>
-  <si>
-    <t>WASM</t>
-  </si>
-  <si>
-    <t>WASM 特定优化</t>
-  </si>
-  <si>
-    <t>WebAssembly 优化</t>
   </si>
   <si>
     <t>WASI 系统调用</t>
@@ -4401,11 +4416,11 @@
       <c r="H72" t="s">
         <v>14</v>
       </c>
-      <c r="I72" s="11" t="s">
+      <c r="I72" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K72" t="s">
         <v>217</v>
-      </c>
-      <c r="K72" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -4422,22 +4437,22 @@
         <v>214</v>
       </c>
       <c r="E73" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="F73" s="9" t="s">
         <v>219</v>
-      </c>
-      <c r="F73" s="9" t="s">
-        <v>220</v>
       </c>
       <c r="G73">
         <v>4</v>
       </c>
       <c r="H73" t="s">
-        <v>221</v>
-      </c>
-      <c r="I73" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K73" t="s">
         <v>217</v>
-      </c>
-      <c r="K73" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -4454,22 +4469,22 @@
         <v>214</v>
       </c>
       <c r="E74" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="F74" s="9" t="s">
         <v>222</v>
-      </c>
-      <c r="F74" s="9" t="s">
-        <v>223</v>
       </c>
       <c r="G74">
         <v>3</v>
       </c>
       <c r="H74" t="s">
-        <v>221</v>
-      </c>
-      <c r="I74" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K74" t="s">
         <v>217</v>
-      </c>
-      <c r="K74" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -4477,19 +4492,19 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
+        <v>223</v>
+      </c>
+      <c r="C75" t="s">
         <v>224</v>
       </c>
-      <c r="C75" t="s">
+      <c r="D75" t="s">
         <v>225</v>
       </c>
-      <c r="D75" t="s">
+      <c r="E75" t="s">
         <v>226</v>
       </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>227</v>
-      </c>
-      <c r="F75" t="s">
-        <v>228</v>
       </c>
       <c r="G75">
         <v>5</v>
@@ -4498,10 +4513,10 @@
         <v>14</v>
       </c>
       <c r="I75" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K75" t="s">
         <v>217</v>
-      </c>
-      <c r="K75" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="76" spans="1:12">
@@ -4509,13 +4524,13 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
+        <v>223</v>
+      </c>
+      <c r="C76" t="s">
         <v>224</v>
       </c>
-      <c r="C76" t="s">
+      <c r="D76" t="s">
         <v>225</v>
-      </c>
-      <c r="D76" t="s">
-        <v>226</v>
       </c>
       <c r="E76" t="s">
         <v>229</v>
@@ -4530,10 +4545,10 @@
         <v>231</v>
       </c>
       <c r="I76" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K76" t="s">
         <v>217</v>
-      </c>
-      <c r="K76" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -4541,13 +4556,13 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
+        <v>223</v>
+      </c>
+      <c r="C77" t="s">
         <v>224</v>
       </c>
-      <c r="C77" t="s">
+      <c r="D77" t="s">
         <v>225</v>
-      </c>
-      <c r="D77" t="s">
-        <v>226</v>
       </c>
       <c r="E77" t="s">
         <v>232</v>
@@ -4562,10 +4577,10 @@
         <v>231</v>
       </c>
       <c r="I77" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K77" t="s">
         <v>217</v>
-      </c>
-      <c r="K77" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -4573,10 +4588,10 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
+        <v>223</v>
+      </c>
+      <c r="C78" t="s">
         <v>224</v>
-      </c>
-      <c r="C78" t="s">
-        <v>225</v>
       </c>
       <c r="D78" t="s">
         <v>234</v>
@@ -4594,10 +4609,10 @@
         <v>14</v>
       </c>
       <c r="I78" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K78" t="s">
         <v>217</v>
-      </c>
-      <c r="K78" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -4605,10 +4620,10 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
+        <v>223</v>
+      </c>
+      <c r="C79" t="s">
         <v>224</v>
-      </c>
-      <c r="C79" t="s">
-        <v>225</v>
       </c>
       <c r="D79" t="s">
         <v>237</v>
@@ -4626,10 +4641,10 @@
         <v>14</v>
       </c>
       <c r="I79" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K79" t="s">
         <v>217</v>
-      </c>
-      <c r="K79" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -4637,10 +4652,10 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
+        <v>223</v>
+      </c>
+      <c r="C80" t="s">
         <v>224</v>
-      </c>
-      <c r="C80" t="s">
-        <v>225</v>
       </c>
       <c r="D80" t="s">
         <v>240</v>
@@ -4658,10 +4673,10 @@
         <v>14</v>
       </c>
       <c r="I80" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K80" t="s">
         <v>217</v>
-      </c>
-      <c r="K80" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -4690,10 +4705,10 @@
         <v>14</v>
       </c>
       <c r="I81" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K81" t="s">
         <v>217</v>
-      </c>
-      <c r="K81" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -4722,10 +4737,10 @@
         <v>14</v>
       </c>
       <c r="I82" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K82" t="s">
         <v>217</v>
-      </c>
-      <c r="K82" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -4754,10 +4769,10 @@
         <v>14</v>
       </c>
       <c r="I83" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K83" t="s">
         <v>217</v>
-      </c>
-      <c r="K83" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -4786,10 +4801,10 @@
         <v>14</v>
       </c>
       <c r="I84" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K84" t="s">
         <v>217</v>
-      </c>
-      <c r="K84" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -4818,10 +4833,10 @@
         <v>257</v>
       </c>
       <c r="I85" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K85" t="s">
         <v>217</v>
-      </c>
-      <c r="K85" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -4850,10 +4865,10 @@
         <v>257</v>
       </c>
       <c r="I86" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K86" t="s">
         <v>217</v>
-      </c>
-      <c r="K86" t="s">
-        <v>218</v>
       </c>
     </row>
   </sheetData>
